--- a/Result/profitability/8107.xlsx
+++ b/Result/profitability/8107.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.57</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1112500000000001</v>
+        <v>0.2737500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>24.12125</v>
+        <v>22.08</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.87</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2550000000000001</v>
+        <v>0.2450000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>22.2475</v>
+        <v>20.08625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.42</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1700000000000001</v>
+        <v>0.3300000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>20.2325</v>
+        <v>17.95</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.19</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2262500000000001</v>
+        <v>0.4137500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>17.94</v>
+        <v>16.24875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.18</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3087500000000001</v>
+        <v>0.4037500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>16.2025</v>
+        <v>14.1275</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2612500000000001</v>
+        <v>0.3950000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>13.33125</v>
+        <v>11.10125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.04</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2625000000000001</v>
+        <v>0.38625</v>
       </c>
       <c r="N8" t="n">
-        <v>10.65125</v>
+        <v>9.47125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0.02000000000000005</v>
       </c>
       <c r="N9" t="n">
-        <v>9.868749999999999</v>
+        <v>9.86875</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>-0.01874999999999992</v>
       </c>
       <c r="N11" t="n">
-        <v>9.072499999999998</v>
+        <v>9.072500000000002</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9796,6 +9796,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8107</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>134</v>
+      </c>
+      <c r="D75" t="n">
+        <v>120</v>
+      </c>
+      <c r="E75" t="n">
+        <v>14</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-36</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-26.77%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>90</v>
+      </c>
+      <c r="J75" t="n">
+        <v>54</v>
+      </c>
+      <c r="K75" t="n">
+        <v>76</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1675000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.83125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="X75" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-9.44</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4813870474247832</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.125</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-13.53</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.570886075949367</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
